--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.1059798555375</v>
+        <v>2.617221726524844</v>
       </c>
       <c r="D2" t="n">
-        <v>47.56246134772461</v>
+        <v>7.72889996900525</v>
       </c>
       <c r="E2" t="n">
-        <v>11.39981598031243</v>
+        <v>1.852470096800769</v>
       </c>
       <c r="F2" t="n">
-        <v>11.80095693543332</v>
+        <v>1.917655502007915</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.58067958581874</v>
+        <v>7.081860432695545</v>
       </c>
       <c r="D3" t="n">
-        <v>13.90173299040201</v>
+        <v>2.259031610940327</v>
       </c>
       <c r="E3" t="n">
-        <v>11.39981598031243</v>
+        <v>1.852470096800769</v>
       </c>
       <c r="F3" t="n">
-        <v>11.80095693543332</v>
+        <v>1.917655502007915</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.00241321693608</v>
+        <v>5.525392147752113</v>
       </c>
       <c r="D4" t="n">
-        <v>30.67925723218042</v>
+        <v>4.985379300229318</v>
       </c>
       <c r="E4" t="n">
-        <v>11.39981598031243</v>
+        <v>1.852470096800769</v>
       </c>
       <c r="F4" t="n">
-        <v>11.80095693543332</v>
+        <v>1.917655502007915</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.74740121029996</v>
+        <v>3.371452696673743</v>
       </c>
       <c r="D5" t="n">
-        <v>35.2840264828483</v>
+        <v>5.733654303462848</v>
       </c>
       <c r="E5" t="n">
-        <v>11.39981598031243</v>
+        <v>1.852470096800769</v>
       </c>
       <c r="F5" t="n">
-        <v>11.80095693543332</v>
+        <v>1.917655502007915</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.5426661856651</v>
+        <v>7.075683255170579</v>
       </c>
       <c r="D6" t="n">
-        <v>43.80091640681187</v>
+        <v>7.117648916106928</v>
       </c>
       <c r="E6" t="n">
-        <v>11.39981598031243</v>
+        <v>1.852470096800769</v>
       </c>
       <c r="F6" t="n">
-        <v>11.80095693543332</v>
+        <v>1.917655502007915</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
